--- a/backtests/VWOB_EMB_2.xlsx
+++ b/backtests/VWOB_EMB_2.xlsx
@@ -15,9 +15,6 @@
   <sheets>
     <sheet name="VWOB_EMB_2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -13437,1629 +13434,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="CWB_ICVT_2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="22">
-          <cell r="BJ22">
-            <v>0</v>
-          </cell>
-          <cell r="BV22">
-            <v>0</v>
-          </cell>
-          <cell r="BY22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="BJ23">
-            <v>0</v>
-          </cell>
-          <cell r="BV23">
-            <v>0</v>
-          </cell>
-          <cell r="BY23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="BJ24">
-            <v>3.4385112415986994E-3</v>
-          </cell>
-          <cell r="BV24">
-            <v>0</v>
-          </cell>
-          <cell r="BY24">
-            <v>3.4385112415986994E-3</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="BJ25">
-            <v>1.3943574559126988E-3</v>
-          </cell>
-          <cell r="BV25">
-            <v>0</v>
-          </cell>
-          <cell r="BY25">
-            <v>1.3943574559126988E-3</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="BJ26">
-            <v>1.0674121281739959E-4</v>
-          </cell>
-          <cell r="BV26">
-            <v>0</v>
-          </cell>
-          <cell r="BY26">
-            <v>1.0674121281739959E-4</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="BJ27">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV27">
-            <v>0</v>
-          </cell>
-          <cell r="BY27">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="BJ28">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV28">
-            <v>0</v>
-          </cell>
-          <cell r="BY28">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="BJ29">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV29">
-            <v>0</v>
-          </cell>
-          <cell r="BY29">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="BJ30">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV30">
-            <v>0</v>
-          </cell>
-          <cell r="BY30">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="BJ31">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV31">
-            <v>0</v>
-          </cell>
-          <cell r="BY31">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="BJ32">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV32">
-            <v>0</v>
-          </cell>
-          <cell r="BY32">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="BJ33">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV33">
-            <v>0</v>
-          </cell>
-          <cell r="BY33">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="BJ34">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV34">
-            <v>0</v>
-          </cell>
-          <cell r="BY34">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="BJ35">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV35">
-            <v>0</v>
-          </cell>
-          <cell r="BY35">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="BJ36">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV36">
-            <v>0</v>
-          </cell>
-          <cell r="BY36">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="BJ37">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV37">
-            <v>0</v>
-          </cell>
-          <cell r="BY37">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="BJ38">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV38">
-            <v>0</v>
-          </cell>
-          <cell r="BY38">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="BJ39">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV39">
-            <v>0</v>
-          </cell>
-          <cell r="BY39">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="BJ40">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV40">
-            <v>0</v>
-          </cell>
-          <cell r="BY40">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="BJ41">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-          <cell r="BV41">
-            <v>0</v>
-          </cell>
-          <cell r="BY41">
-            <v>4.1787788822000996E-3</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="BJ42">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV42">
-            <v>0</v>
-          </cell>
-          <cell r="BY42">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="BJ43">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV43">
-            <v>0</v>
-          </cell>
-          <cell r="BY43">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="BJ44">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV44">
-            <v>0</v>
-          </cell>
-          <cell r="BY44">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="BJ45">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV45">
-            <v>0</v>
-          </cell>
-          <cell r="BY45">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="BJ46">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV46">
-            <v>0</v>
-          </cell>
-          <cell r="BY46">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="BJ47">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV47">
-            <v>0</v>
-          </cell>
-          <cell r="BY47">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="BJ48">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV48">
-            <v>0</v>
-          </cell>
-          <cell r="BY48">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="BJ49">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV49">
-            <v>0</v>
-          </cell>
-          <cell r="BY49">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="BJ50">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV50">
-            <v>0</v>
-          </cell>
-          <cell r="BY50">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="BJ51">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV51">
-            <v>0</v>
-          </cell>
-          <cell r="BY51">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="BJ52">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV52">
-            <v>0</v>
-          </cell>
-          <cell r="BY52">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="BJ53">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV53">
-            <v>0</v>
-          </cell>
-          <cell r="BY53">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="BJ54">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV54">
-            <v>0</v>
-          </cell>
-          <cell r="BY54">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="BJ55">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV55">
-            <v>0</v>
-          </cell>
-          <cell r="BY55">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="BJ56">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV56">
-            <v>0</v>
-          </cell>
-          <cell r="BY56">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="BJ57">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV57">
-            <v>0</v>
-          </cell>
-          <cell r="BY57">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="BJ58">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV58">
-            <v>0</v>
-          </cell>
-          <cell r="BY58">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="BJ59">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV59">
-            <v>0</v>
-          </cell>
-          <cell r="BY59">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="BJ60">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-          <cell r="BV60">
-            <v>0</v>
-          </cell>
-          <cell r="BY60">
-            <v>8.5207067177144012E-3</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="BJ61">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV61">
-            <v>0</v>
-          </cell>
-          <cell r="BY61">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="BJ62">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV62">
-            <v>0</v>
-          </cell>
-          <cell r="BY62">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="BJ63">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV63">
-            <v>0</v>
-          </cell>
-          <cell r="BY63">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="BJ64">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV64">
-            <v>0</v>
-          </cell>
-          <cell r="BY64">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="BJ65">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV65">
-            <v>0</v>
-          </cell>
-          <cell r="BY65">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="BJ66">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV66">
-            <v>0</v>
-          </cell>
-          <cell r="BY66">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="BJ67">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV67">
-            <v>0</v>
-          </cell>
-          <cell r="BY67">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="BJ68">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV68">
-            <v>0</v>
-          </cell>
-          <cell r="BY68">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="BJ69">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV69">
-            <v>0</v>
-          </cell>
-          <cell r="BY69">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="BJ70">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV70">
-            <v>0</v>
-          </cell>
-          <cell r="BY70">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="BJ71">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV71">
-            <v>1.3210643006825607E-3</v>
-          </cell>
-          <cell r="BY71">
-            <v>1.8132397656742023E-2</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="BJ72">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV72">
-            <v>4.034665793740711E-3</v>
-          </cell>
-          <cell r="BY72">
-            <v>2.0845999149800173E-2</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="BJ73">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV73">
-            <v>4.034665793740711E-3</v>
-          </cell>
-          <cell r="BY73">
-            <v>2.0845999149800173E-2</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="BJ74">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV74">
-            <v>8.0507079795472322E-3</v>
-          </cell>
-          <cell r="BY74">
-            <v>2.4862041335606693E-2</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="BJ75">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV75">
-            <v>8.0507079795472322E-3</v>
-          </cell>
-          <cell r="BY75">
-            <v>2.4862041335606693E-2</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="BJ76">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV76">
-            <v>8.0507079795472322E-3</v>
-          </cell>
-          <cell r="BY76">
-            <v>2.4862041335606693E-2</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="BJ77">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV77">
-            <v>8.0507079795472322E-3</v>
-          </cell>
-          <cell r="BY77">
-            <v>2.4862041335606693E-2</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="BJ78">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV78">
-            <v>8.0507079795472322E-3</v>
-          </cell>
-          <cell r="BY78">
-            <v>2.4862041335606693E-2</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="BJ79">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV79">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY79">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="BJ80">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV80">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY80">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="BJ81">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV81">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY81">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="BJ82">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV82">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY82">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="BJ83">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV83">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY83">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="BJ84">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV84">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY84">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="BJ85">
-            <v>1.6811333356059461E-2</v>
-          </cell>
-          <cell r="BV85">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY85">
-            <v>2.7855951389236834E-2</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="BJ86">
-            <v>1.996650664977466E-2</v>
-          </cell>
-          <cell r="BV86">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY86">
-            <v>3.1011124682952033E-2</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="BJ87">
-            <v>1.996650664977466E-2</v>
-          </cell>
-          <cell r="BV87">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY87">
-            <v>3.1011124682952033E-2</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="BJ88">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV88">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY88">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="BJ89">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV89">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY89">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="BJ90">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV90">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY90">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="BJ91">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV91">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY91">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="BJ92">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV92">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY92">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="BJ93">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV93">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY93">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="BJ94">
-            <v>2.2591591880305462E-2</v>
-          </cell>
-          <cell r="BV94">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY94">
-            <v>3.3636209913482831E-2</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="BJ95">
-            <v>2.2512236556081963E-2</v>
-          </cell>
-          <cell r="BV95">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY95">
-            <v>3.3556854589259333E-2</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="BJ96">
-            <v>2.4681547557358845E-2</v>
-          </cell>
-          <cell r="BV96">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY96">
-            <v>3.5726165590536214E-2</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="BJ97">
-            <v>2.4681547557358845E-2</v>
-          </cell>
-          <cell r="BV97">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY97">
-            <v>3.5726165590536214E-2</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="BJ98">
-            <v>2.4681547557358845E-2</v>
-          </cell>
-          <cell r="BV98">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY98">
-            <v>3.5726165590536214E-2</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="BJ99">
-            <v>2.4681547557358845E-2</v>
-          </cell>
-          <cell r="BV99">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY99">
-            <v>3.5726165590536214E-2</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="BJ100">
-            <v>2.4681547557358845E-2</v>
-          </cell>
-          <cell r="BV100">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY100">
-            <v>3.5726165590536214E-2</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="BJ101">
-            <v>2.5845698767138228E-2</v>
-          </cell>
-          <cell r="BV101">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY101">
-            <v>3.6890316800315598E-2</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="BJ102">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV102">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY102">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="BJ103">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV103">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY103">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="BJ104">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV104">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY104">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="BJ105">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV105">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY105">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="BJ106">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV106">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY106">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="BJ107">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV107">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY107">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="BJ108">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV108">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY108">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="BJ109">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV109">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY109">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="BJ110">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV110">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY110">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="BJ111">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV111">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY111">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="BJ112">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV112">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY112">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="BJ113">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV113">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY113">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="BJ114">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV114">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY114">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="BJ115">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV115">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY115">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="BJ116">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV116">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY116">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="BJ117">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV117">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY117">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="BJ118">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV118">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY118">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="BJ119">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV119">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY119">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="BJ120">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV120">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY120">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="BJ121">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV121">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY121">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="BJ122">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV122">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY122">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="BJ123">
-            <v>2.9482639521364058E-2</v>
-          </cell>
-          <cell r="BV123">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY123">
-            <v>4.0527257554541424E-2</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="BJ124">
-            <v>2.8140859557766358E-2</v>
-          </cell>
-          <cell r="BV124">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY124">
-            <v>3.9185477590943721E-2</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="BJ125">
-            <v>2.8140859557766358E-2</v>
-          </cell>
-          <cell r="BV125">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY125">
-            <v>3.9185477590943721E-2</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="BJ126">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV126">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY126">
-            <v>4.2088580528682522E-2</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="BJ127">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV127">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY127">
-            <v>4.2088580528682522E-2</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="BJ128">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV128">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY128">
-            <v>4.2088580528682522E-2</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="BJ129">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV129">
-            <v>1.1044618033177373E-2</v>
-          </cell>
-          <cell r="BY129">
-            <v>4.2088580528682522E-2</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="BJ130">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV130">
-            <v>1.4380019370490554E-2</v>
-          </cell>
-          <cell r="BY130">
-            <v>4.5423981865995701E-2</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="BJ131">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV131">
-            <v>1.4380019370490554E-2</v>
-          </cell>
-          <cell r="BY131">
-            <v>4.5423981865995701E-2</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="BJ132">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV132">
-            <v>1.4380019370490554E-2</v>
-          </cell>
-          <cell r="BY132">
-            <v>4.5423981865995701E-2</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="BJ133">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV133">
-            <v>1.4380019370490554E-2</v>
-          </cell>
-          <cell r="BY133">
-            <v>4.5423981865995701E-2</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="BJ134">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV134">
-            <v>1.4773607209856605E-2</v>
-          </cell>
-          <cell r="BY134">
-            <v>4.5817569705361751E-2</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="BJ135">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV135">
-            <v>1.4294956952806605E-2</v>
-          </cell>
-          <cell r="BY135">
-            <v>4.5338919448311754E-2</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="BJ136">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV136">
-            <v>1.5579086591429467E-2</v>
-          </cell>
-          <cell r="BY136">
-            <v>4.6623049086934612E-2</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="BJ137">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV137">
-            <v>1.6018640867893646E-2</v>
-          </cell>
-          <cell r="BY137">
-            <v>4.7062603363398792E-2</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="BJ138">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV138">
-            <v>1.9996441817846045E-2</v>
-          </cell>
-          <cell r="BY138">
-            <v>5.104040431335119E-2</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="BJ139">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV139">
-            <v>1.9996441817846045E-2</v>
-          </cell>
-          <cell r="BY139">
-            <v>5.104040431335119E-2</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="BJ140">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV140">
-            <v>1.9996441817846045E-2</v>
-          </cell>
-          <cell r="BY140">
-            <v>5.104040431335119E-2</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="BJ141">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV141">
-            <v>1.9996441817846045E-2</v>
-          </cell>
-          <cell r="BY141">
-            <v>5.104040431335119E-2</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="BJ142">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV142">
-            <v>1.9996441817846045E-2</v>
-          </cell>
-          <cell r="BY142">
-            <v>5.104040431335119E-2</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="BJ143">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV143">
-            <v>1.9996441817846045E-2</v>
-          </cell>
-          <cell r="BY143">
-            <v>5.104040431335119E-2</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="BJ144">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV144">
-            <v>1.9641605696182843E-2</v>
-          </cell>
-          <cell r="BY144">
-            <v>5.0685568191687985E-2</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="BJ145">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV145">
-            <v>2.1798480755228743E-2</v>
-          </cell>
-          <cell r="BY145">
-            <v>5.2842443250733881E-2</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="BJ146">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV146">
-            <v>1.6933748972931394E-2</v>
-          </cell>
-          <cell r="BY146">
-            <v>4.7977711468436532E-2</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="BJ147">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV147">
-            <v>1.6933748972931394E-2</v>
-          </cell>
-          <cell r="BY147">
-            <v>4.7977711468436532E-2</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="BJ148">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV148">
-            <v>1.4593842134356994E-2</v>
-          </cell>
-          <cell r="BY148">
-            <v>4.5637804629862132E-2</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="BJ149">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV149">
-            <v>1.5393886927251193E-2</v>
-          </cell>
-          <cell r="BY149">
-            <v>4.6437849422756333E-2</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="BJ150">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV150">
-            <v>1.6131080581748693E-2</v>
-          </cell>
-          <cell r="BY150">
-            <v>4.7175043077253835E-2</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="BJ151">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV151">
-            <v>1.6726154643626603E-2</v>
-          </cell>
-          <cell r="BY151">
-            <v>4.7770117139131749E-2</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="BJ152">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV152">
-            <v>1.4197861155556513E-2</v>
-          </cell>
-          <cell r="BY152">
-            <v>4.5241823651061656E-2</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="BJ153">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV153">
-            <v>1.5961160268846E-2</v>
-          </cell>
-          <cell r="BY153">
-            <v>4.7005122764351141E-2</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="BJ154">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV154">
-            <v>1.94114505485335E-2</v>
-          </cell>
-          <cell r="BY154">
-            <v>5.0455413044038638E-2</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="BJ155">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV155">
-            <v>1.94114505485335E-2</v>
-          </cell>
-          <cell r="BY155">
-            <v>5.0455413044038638E-2</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="BJ156">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV156">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY156">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="BJ157">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV157">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY157">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="BJ158">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV158">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY158">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="BJ159">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV159">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY159">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="BJ160">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV160">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY160">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="BJ161">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV161">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY161">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="BJ162">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV162">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY162">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="BJ163">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV163">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY163">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="BJ164">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV164">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY164">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="BJ165">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV165">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY165">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="BJ166">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV166">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY166">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="BJ167">
-            <v>3.1043962495505159E-2</v>
-          </cell>
-          <cell r="BV167">
-            <v>2.165896884963019E-2</v>
-          </cell>
-          <cell r="BY167">
-            <v>5.2702931345135332E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -15377,7 +13751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7A461E-E8D1-4854-B9FC-F31A5316BC18}">
-  <dimension ref="A1:XFD167"/>
+  <dimension ref="A1:CX167"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -17126,7 +15500,7 @@
         <v>-4.7483385964414198E-4</v>
       </c>
       <c r="CL17" s="15">
-        <f t="shared" ref="CL17:CL23" si="3">CL16+0.0005</f>
+        <f t="shared" ref="CL17:CL22" si="3">CL16+0.0005</f>
         <v>1E-3</v>
       </c>
       <c r="CM17" s="16">
